--- a/data/EEZ_037/EEZ_037.xlsx
+++ b/data/EEZ_037/EEZ_037.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,85 +532,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>17</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1952-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>catch_tonnes</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ppr_tonnes</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ppr_over_npp_percent</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -598,10 +620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -609,10 +631,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1958</v>
+        <v>1954</v>
       </c>
       <c r="B17" t="n">
-        <v>0.025</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -620,10 +642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B18" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -631,10 +653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -642,10 +664,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1965</v>
+        <v>1959</v>
       </c>
       <c r="B20" t="n">
-        <v>0.013</v>
+        <v>0.029</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -653,10 +675,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -664,10 +686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B22" t="n">
-        <v>117.722</v>
+        <v>0.013</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -675,10 +697,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B23" t="n">
-        <v>196.236</v>
+        <v>0.007</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -686,10 +708,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B24" t="n">
-        <v>198.135</v>
+        <v>117.722</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -697,10 +719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B25" t="n">
-        <v>203.614</v>
+        <v>196.236</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -708,10 +730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B26" t="n">
-        <v>963.996</v>
+        <v>198.135</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -719,10 +741,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B27" t="n">
-        <v>1265.347</v>
+        <v>203.614</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -730,10 +752,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B28" t="n">
-        <v>1385.018</v>
+        <v>963.996</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -741,10 +763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B29" t="n">
-        <v>2021.928</v>
+        <v>1265.347</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -752,10 +774,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B30" t="n">
-        <v>569.54</v>
+        <v>1385.018</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -763,10 +785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B31" t="n">
-        <v>1186.308</v>
+        <v>2021.928</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -774,10 +796,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B32" t="n">
-        <v>1843.531</v>
+        <v>569.54</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -785,10 +807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B33" t="n">
-        <v>1528.155</v>
+        <v>1186.308</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -796,10 +818,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1989</v>
+        <v>1977</v>
       </c>
       <c r="B34" t="n">
-        <v>0.122</v>
+        <v>1843.531</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -807,271 +829,271 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1994</v>
+        <v>1978</v>
       </c>
       <c r="B35" t="n">
-        <v>725</v>
+        <v>1528.155</v>
       </c>
       <c r="C35" t="n">
-        <v>638407.588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1995</v>
+        <v>1989</v>
       </c>
       <c r="B36" t="n">
-        <v>725</v>
+        <v>0.122</v>
       </c>
       <c r="C36" t="n">
-        <v>638407.588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B37" t="n">
-        <v>517.8</v>
+        <v>725</v>
       </c>
       <c r="C37" t="n">
-        <v>456005.42</v>
+        <v>638407.588</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B38" t="n">
-        <v>854.46</v>
+        <v>725</v>
       </c>
       <c r="C38" t="n">
-        <v>752408.942</v>
+        <v>638407.588</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B39" t="n">
-        <v>310.7</v>
+        <v>517.8</v>
       </c>
       <c r="C39" t="n">
-        <v>273603.252</v>
+        <v>456005.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B40" t="n">
-        <v>80</v>
+        <v>854.46</v>
       </c>
       <c r="C40" t="n">
-        <v>72960.867</v>
+        <v>752408.942</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B41" t="n">
-        <v>35</v>
+        <v>310.7</v>
       </c>
       <c r="C41" t="n">
-        <v>31920.379</v>
+        <v>273603.252</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B42" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C42" t="n">
-        <v>36480.434</v>
+        <v>72960.867</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B43" t="n">
-        <v>39.728</v>
+        <v>35</v>
       </c>
       <c r="C43" t="n">
-        <v>36232.768</v>
+        <v>31920.379</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B44" t="n">
-        <v>353.671</v>
+        <v>40</v>
       </c>
       <c r="C44" t="n">
-        <v>322551.466</v>
+        <v>36480.434</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B45" t="n">
-        <v>55.74</v>
+        <v>39.728</v>
       </c>
       <c r="C45" t="n">
-        <v>50835.484</v>
+        <v>36232.768</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B46" t="n">
-        <v>248.845</v>
+        <v>353.671</v>
       </c>
       <c r="C46" t="n">
-        <v>226949.657</v>
+        <v>322551.466</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B47" t="n">
-        <v>321.416</v>
+        <v>55.74</v>
       </c>
       <c r="C47" t="n">
-        <v>293135.14</v>
+        <v>50835.484</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B48" t="n">
-        <v>389.935</v>
+        <v>248.845</v>
       </c>
       <c r="C48" t="n">
-        <v>355624.655</v>
+        <v>226949.657</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B49" t="n">
-        <v>516.826</v>
+        <v>321.416</v>
       </c>
       <c r="C49" t="n">
-        <v>471351.343</v>
+        <v>293135.14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B50" t="n">
-        <v>263.802</v>
+        <v>389.935</v>
       </c>
       <c r="C50" t="n">
-        <v>240590.283</v>
+        <v>355624.655</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B51" t="n">
-        <v>314.462</v>
+        <v>516.826</v>
       </c>
       <c r="C51" t="n">
-        <v>286792.774</v>
+        <v>471351.343</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B52" t="n">
-        <v>302.983</v>
+        <v>263.802</v>
       </c>
       <c r="C52" t="n">
-        <v>276324.139</v>
+        <v>240590.283</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B53" t="n">
-        <v>368.849</v>
+        <v>314.462</v>
       </c>
       <c r="C53" t="n">
-        <v>336394.401</v>
+        <v>286792.774</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B54" t="n">
-        <v>408.845</v>
+        <v>302.983</v>
       </c>
       <c r="C54" t="n">
-        <v>372871.072</v>
+        <v>276324.139</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B55" t="n">
-        <v>324.449</v>
+        <v>368.849</v>
       </c>
       <c r="C55" t="n">
-        <v>295901.005</v>
+        <v>336394.401</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B56" t="n">
-        <v>434.33</v>
+        <v>408.845</v>
       </c>
       <c r="C56" t="n">
-        <v>396113.668</v>
+        <v>372871.072</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B57" t="n">
-        <v>434.33</v>
+        <v>324.449</v>
       </c>
       <c r="C57" t="n">
-        <v>396113.668</v>
+        <v>295901.005</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B58" t="n">
         <v>434.33</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>396113.668</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B59" t="n">
         <v>434.33</v>
@@ -1080,8 +1102,37 @@
         <v>396113.668</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B60" t="n">
+        <v>434.33</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B61" t="n">
+        <v>434.33</v>
+      </c>
+      <c r="C61" t="n">
+        <v>396113.668</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
         </is>
@@ -1175,240 +1226,146 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AY1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1957</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1959</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1962</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1965</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1966</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1967</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1968</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1972</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -4267,6 +4224,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4399,240 +4595,146 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1954</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1957</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1959</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1965</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1966</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1967</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1972</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -4791,7 +4893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/EEZ_037/EEZ_037.xlsx
+++ b/data/EEZ_037/EEZ_037.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$51</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -903,6 +906,9 @@
       <c r="C41" t="n">
         <v>273603.252</v>
       </c>
+      <c r="D41" t="n">
+        <v>0.1026</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -914,6 +920,9 @@
       <c r="C42" t="n">
         <v>72960.867</v>
       </c>
+      <c r="D42" t="n">
+        <v>0.0273</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -925,6 +934,9 @@
       <c r="C43" t="n">
         <v>31920.379</v>
       </c>
+      <c r="D43" t="n">
+        <v>0.0125</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -936,6 +948,9 @@
       <c r="C44" t="n">
         <v>36480.434</v>
       </c>
+      <c r="D44" t="n">
+        <v>0.0142</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -947,6 +962,9 @@
       <c r="C45" t="n">
         <v>36232.768</v>
       </c>
+      <c r="D45" t="n">
+        <v>0.0131</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -958,6 +976,9 @@
       <c r="C46" t="n">
         <v>322551.466</v>
       </c>
+      <c r="D46" t="n">
+        <v>0.1135</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -969,6 +990,9 @@
       <c r="C47" t="n">
         <v>50835.484</v>
       </c>
+      <c r="D47" t="n">
+        <v>0.0171</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -980,6 +1004,9 @@
       <c r="C48" t="n">
         <v>226949.657</v>
       </c>
+      <c r="D48" t="n">
+        <v>0.082</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -991,6 +1018,9 @@
       <c r="C49" t="n">
         <v>293135.14</v>
       </c>
+      <c r="D49" t="n">
+        <v>0.1067</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1002,6 +1032,9 @@
       <c r="C50" t="n">
         <v>355624.655</v>
       </c>
+      <c r="D50" t="n">
+        <v>0.1293</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1013,6 +1046,9 @@
       <c r="C51" t="n">
         <v>471351.343</v>
       </c>
+      <c r="D51" t="n">
+        <v>0.167</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1024,6 +1060,9 @@
       <c r="C52" t="n">
         <v>240590.283</v>
       </c>
+      <c r="D52" t="n">
+        <v>0.0806</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1035,6 +1074,9 @@
       <c r="C53" t="n">
         <v>286792.774</v>
       </c>
+      <c r="D53" t="n">
+        <v>0.1044</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1046,6 +1088,9 @@
       <c r="C54" t="n">
         <v>276324.139</v>
       </c>
+      <c r="D54" t="n">
+        <v>0.1054</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1057,6 +1102,9 @@
       <c r="C55" t="n">
         <v>336394.401</v>
       </c>
+      <c r="D55" t="n">
+        <v>0.1232</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1068,6 +1116,9 @@
       <c r="C56" t="n">
         <v>372871.072</v>
       </c>
+      <c r="D56" t="n">
+        <v>0.1329</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1079,6 +1130,9 @@
       <c r="C57" t="n">
         <v>295901.005</v>
       </c>
+      <c r="D57" t="n">
+        <v>0.1082</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1090,6 +1144,9 @@
       <c r="C58" t="n">
         <v>396113.668</v>
       </c>
+      <c r="D58" t="n">
+        <v>0.1494</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1101,6 +1158,9 @@
       <c r="C59" t="n">
         <v>396113.668</v>
       </c>
+      <c r="D59" t="n">
+        <v>0.134</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1112,6 +1172,9 @@
       <c r="C60" t="n">
         <v>0</v>
       </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1123,22 +1186,1820 @@
       <c r="C61" t="n">
         <v>396113.668</v>
       </c>
+      <c r="D61" t="n">
+        <v>0.1268</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1952</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1957</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1965</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1966</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1967</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1970</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1971</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1972</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29630505.02078108</v>
+      </c>
+      <c r="G30" t="n">
+        <v>29630505.02078108</v>
+      </c>
+      <c r="H30" t="n">
+        <v>29630505.02078108</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29630505.02078108</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29706778.92989187</v>
+      </c>
+      <c r="G31" t="n">
+        <v>29706778.92989187</v>
+      </c>
+      <c r="H31" t="n">
+        <v>29706778.92989187</v>
+      </c>
+      <c r="I31" t="n">
+        <v>29706778.92989187</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B32" t="n">
+        <v>28458406.37915348</v>
+      </c>
+      <c r="G32" t="n">
+        <v>28458406.37915348</v>
+      </c>
+      <c r="H32" t="n">
+        <v>28458406.37915348</v>
+      </c>
+      <c r="I32" t="n">
+        <v>28458406.37915348</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>28595811.21295504</v>
+      </c>
+      <c r="G33" t="n">
+        <v>28595811.21295504</v>
+      </c>
+      <c r="H33" t="n">
+        <v>28595811.21295504</v>
+      </c>
+      <c r="I33" t="n">
+        <v>28595811.21295504</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B34" t="n">
+        <v>30807516.47384891</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30807516.47384891</v>
+      </c>
+      <c r="H34" t="n">
+        <v>30807516.47384891</v>
+      </c>
+      <c r="I34" t="n">
+        <v>30807516.47384891</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B35" t="n">
+        <v>30949929.72126472</v>
+      </c>
+      <c r="C35" t="n">
+        <v>32229245.11162106</v>
+      </c>
+      <c r="D35" t="n">
+        <v>19926219.43020404</v>
+      </c>
+      <c r="E35" t="n">
+        <v>36594639.31131992</v>
+      </c>
+      <c r="F35" t="n">
+        <v>51333091.89732283</v>
+      </c>
+      <c r="G35" t="n">
+        <v>32229245.11162106</v>
+      </c>
+      <c r="H35" t="n">
+        <v>19926219.43020404</v>
+      </c>
+      <c r="I35" t="n">
+        <v>51333091.89732283</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B36" t="n">
+        <v>31156004.94043149</v>
+      </c>
+      <c r="C36" t="n">
+        <v>31563376.19518774</v>
+      </c>
+      <c r="D36" t="n">
+        <v>19664735.67724879</v>
+      </c>
+      <c r="E36" t="n">
+        <v>39035066.14329923</v>
+      </c>
+      <c r="F36" t="n">
+        <v>51118394.2198281</v>
+      </c>
+      <c r="G36" t="n">
+        <v>31563376.19518774</v>
+      </c>
+      <c r="H36" t="n">
+        <v>19664735.67724879</v>
+      </c>
+      <c r="I36" t="n">
+        <v>51118394.2198281</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B37" t="n">
+        <v>32348792.79745362</v>
+      </c>
+      <c r="C37" t="n">
+        <v>33084543.22798357</v>
+      </c>
+      <c r="D37" t="n">
+        <v>20461104.61281974</v>
+      </c>
+      <c r="E37" t="n">
+        <v>38422906.70066383</v>
+      </c>
+      <c r="F37" t="n">
+        <v>49848777.90608173</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33084543.22798357</v>
+      </c>
+      <c r="H37" t="n">
+        <v>20461104.61281974</v>
+      </c>
+      <c r="I37" t="n">
+        <v>49848777.90608173</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B38" t="n">
+        <v>29727332.30129702</v>
+      </c>
+      <c r="C38" t="n">
+        <v>30738860.69163786</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19101564.19774229</v>
+      </c>
+      <c r="E38" t="n">
+        <v>35998862.61044104</v>
+      </c>
+      <c r="F38" t="n">
+        <v>47004827.80615652</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30738860.69163786</v>
+      </c>
+      <c r="H38" t="n">
+        <v>19101564.19774229</v>
+      </c>
+      <c r="I38" t="n">
+        <v>47004827.80615652</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B39" t="n">
+        <v>30153433.74412638</v>
+      </c>
+      <c r="C39" t="n">
+        <v>30522104.79039805</v>
+      </c>
+      <c r="D39" t="n">
+        <v>18870812.33897707</v>
+      </c>
+      <c r="E39" t="n">
+        <v>37367762.1047223</v>
+      </c>
+      <c r="F39" t="n">
+        <v>46780260.09499418</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30522104.79039805</v>
+      </c>
+      <c r="H39" t="n">
+        <v>18870812.33897707</v>
+      </c>
+      <c r="I39" t="n">
+        <v>46780260.09499418</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B40" t="n">
+        <v>29174027.33970987</v>
+      </c>
+      <c r="C40" t="n">
+        <v>30557859.78536401</v>
+      </c>
+      <c r="D40" t="n">
+        <v>18946723.5441276</v>
+      </c>
+      <c r="E40" t="n">
+        <v>34863078.94454198</v>
+      </c>
+      <c r="F40" t="n">
+        <v>46731817.25745974</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30557859.78536401</v>
+      </c>
+      <c r="H40" t="n">
+        <v>18946723.5441276</v>
+      </c>
+      <c r="I40" t="n">
+        <v>46731817.25745974</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B41" t="n">
+        <v>29843674.02647112</v>
+      </c>
+      <c r="C41" t="n">
+        <v>31367574.42620746</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19438013.43192825</v>
+      </c>
+      <c r="E41" t="n">
+        <v>35728913.07291086</v>
+      </c>
+      <c r="F41" t="n">
+        <v>48685675.86138415</v>
+      </c>
+      <c r="G41" t="n">
+        <v>31367574.42620746</v>
+      </c>
+      <c r="H41" t="n">
+        <v>19438013.43192825</v>
+      </c>
+      <c r="I41" t="n">
+        <v>48685675.86138415</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B42" t="n">
+        <v>31776209.96714583</v>
+      </c>
+      <c r="C42" t="n">
+        <v>33146035.89900102</v>
+      </c>
+      <c r="D42" t="n">
+        <v>20500724.338608</v>
+      </c>
+      <c r="E42" t="n">
+        <v>37116675.99038654</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51107885.08154965</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33146035.89900102</v>
+      </c>
+      <c r="H42" t="n">
+        <v>20500724.338608</v>
+      </c>
+      <c r="I42" t="n">
+        <v>51107885.08154965</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B43" t="n">
+        <v>28457213.03434826</v>
+      </c>
+      <c r="C43" t="n">
+        <v>30509739.94862973</v>
+      </c>
+      <c r="D43" t="n">
+        <v>18702650.3479687</v>
+      </c>
+      <c r="E43" t="n">
+        <v>36550146.63381483</v>
+      </c>
+      <c r="F43" t="n">
+        <v>50640475.56265096</v>
+      </c>
+      <c r="G43" t="n">
+        <v>30509739.94862973</v>
+      </c>
+      <c r="H43" t="n">
+        <v>18702650.3479687</v>
+      </c>
+      <c r="I43" t="n">
+        <v>50640475.56265096</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B44" t="n">
+        <v>26823218.02299392</v>
+      </c>
+      <c r="C44" t="n">
+        <v>29116482.30894297</v>
+      </c>
+      <c r="D44" t="n">
+        <v>17747024.39387025</v>
+      </c>
+      <c r="E44" t="n">
+        <v>34438486.48023696</v>
+      </c>
+      <c r="F44" t="n">
+        <v>47928808.12135753</v>
+      </c>
+      <c r="G44" t="n">
+        <v>29116482.30894297</v>
+      </c>
+      <c r="H44" t="n">
+        <v>17747024.39387025</v>
+      </c>
+      <c r="I44" t="n">
+        <v>47928808.12135753</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B45" t="n">
+        <v>28162077.43735096</v>
+      </c>
+      <c r="C45" t="n">
+        <v>30349358.08893908</v>
+      </c>
+      <c r="D45" t="n">
+        <v>18685585.782834</v>
+      </c>
+      <c r="E45" t="n">
+        <v>37230936.90019514</v>
+      </c>
+      <c r="F45" t="n">
+        <v>47234495.49021331</v>
+      </c>
+      <c r="G45" t="n">
+        <v>30349358.08893908</v>
+      </c>
+      <c r="H45" t="n">
+        <v>18685585.782834</v>
+      </c>
+      <c r="I45" t="n">
+        <v>47234495.49021331</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B46" t="n">
+        <v>28569385.56747431</v>
+      </c>
+      <c r="C46" t="n">
+        <v>31165018.42323379</v>
+      </c>
+      <c r="D46" t="n">
+        <v>19215933.15364612</v>
+      </c>
+      <c r="E46" t="n">
+        <v>35547700.904551</v>
+      </c>
+      <c r="F46" t="n">
+        <v>48421065.1104789</v>
+      </c>
+      <c r="G46" t="n">
+        <v>31165018.42323379</v>
+      </c>
+      <c r="H46" t="n">
+        <v>19215933.15364612</v>
+      </c>
+      <c r="I46" t="n">
+        <v>48421065.1104789</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>5</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B47" t="n">
+        <v>28245739.3761313</v>
+      </c>
+      <c r="C47" t="n">
+        <v>30380890.48431834</v>
+      </c>
+      <c r="D47" t="n">
+        <v>18816528.0578878</v>
+      </c>
+      <c r="E47" t="n">
+        <v>32602435.33682583</v>
+      </c>
+      <c r="F47" t="n">
+        <v>46211169.03512114</v>
+      </c>
+      <c r="G47" t="n">
+        <v>30380890.48431834</v>
+      </c>
+      <c r="H47" t="n">
+        <v>18816528.0578878</v>
+      </c>
+      <c r="I47" t="n">
+        <v>46211169.03512114</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B48" t="n">
+        <v>26851308.89123274</v>
+      </c>
+      <c r="C48" t="n">
+        <v>29453175.25311076</v>
+      </c>
+      <c r="D48" t="n">
+        <v>18000467.59493308</v>
+      </c>
+      <c r="E48" t="n">
+        <v>39119491.68454148</v>
+      </c>
+      <c r="F48" t="n">
+        <v>44512681.26519366</v>
+      </c>
+      <c r="G48" t="n">
+        <v>29453175.25311076</v>
+      </c>
+      <c r="H48" t="n">
+        <v>18000467.59493308</v>
+      </c>
+      <c r="I48" t="n">
+        <v>44512681.26519366</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B49" t="n">
+        <v>27604242.69717695</v>
+      </c>
+      <c r="C49" t="n">
+        <v>32852860.03163959</v>
+      </c>
+      <c r="D49" t="n">
+        <v>20142629.65984107</v>
+      </c>
+      <c r="E49" t="n">
+        <v>37217832.60086691</v>
+      </c>
+      <c r="F49" t="n">
+        <v>48723674.44913361</v>
+      </c>
+      <c r="G49" t="n">
+        <v>32852860.03163959</v>
+      </c>
+      <c r="H49" t="n">
+        <v>20142629.65984107</v>
+      </c>
+      <c r="I49" t="n">
+        <v>48723674.44913361</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>5</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B50" t="n">
+        <v>28888453.45811238</v>
+      </c>
+      <c r="C50" t="n">
+        <v>32944352.99459008</v>
+      </c>
+      <c r="D50" t="n">
+        <v>20316924.00309497</v>
+      </c>
+      <c r="E50" t="n">
+        <v>38567323.46933428</v>
+      </c>
+      <c r="F50" t="n">
+        <v>50072725.9373785</v>
+      </c>
+      <c r="G50" t="n">
+        <v>32944352.99459008</v>
+      </c>
+      <c r="H50" t="n">
+        <v>20316924.00309497</v>
+      </c>
+      <c r="I50" t="n">
+        <v>50072725.9373785</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B51" t="n">
+        <v>28929996.45080489</v>
+      </c>
+      <c r="C51" t="n">
+        <v>34707511.48218951</v>
+      </c>
+      <c r="D51" t="n">
+        <v>21407641.5954359</v>
+      </c>
+      <c r="E51" t="n">
+        <v>38856825.4544799</v>
+      </c>
+      <c r="F51" t="n">
+        <v>53460481.03263792</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34707511.48218951</v>
+      </c>
+      <c r="H51" t="n">
+        <v>21407641.5954359</v>
+      </c>
+      <c r="I51" t="n">
+        <v>53460481.03263792</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4150,71 +6011,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for EEZ_037</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dissostichus eleginoides</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="C5" t="n">
-        <v>912.010839</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -4229,43 +6042,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for EEZ_037</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Dissostichus eleginoides</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="C5" t="n">
+        <v>912.010839</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -4290,14 +6131,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -4341,14 +6182,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -4377,6 +6218,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4462,7 +6354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4891,32 +6783,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No net primary production estimate is available for this ecosystem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NPP currently covers LME and High Seas units only, not EEZs.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>